--- a/data/Date_Sector_Monetar.xlsx
+++ b/data/Date_Sector_Monetar.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\!MDED\Comert exterior\COD_PAGE\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBC9419-5B04-4C77-B16F-DE26D98BCA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF48903B-4DDD-4F36-8428-1B47623B2D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4275" yWindow="4275" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monetar" sheetId="6" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>An</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>Baza monetară, mil. lei</t>
-  </si>
-  <si>
-    <t>PIB, mil lei</t>
   </si>
   <si>
     <t>Depozite</t>
@@ -330,535 +327,473 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1F3D593-26F1-4FE7-A4DD-FD5D8594C31E}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="2"/>
+    <col min="2" max="2" width="25.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2000</v>
       </c>
-      <c r="B2" s="3">
-        <v>16020</v>
+      <c r="B2" s="4">
+        <v>18.399999999999999</v>
       </c>
       <c r="C2" s="4">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="D2" s="4">
         <v>222.64</v>
       </c>
+      <c r="D2" s="3">
+        <v>1945.7</v>
+      </c>
       <c r="E2" s="3">
-        <v>1945.7</v>
-      </c>
-      <c r="F2" s="3">
         <v>2040.2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2001</v>
       </c>
-      <c r="B3" s="3">
-        <v>19052</v>
+      <c r="B3" s="4">
+        <v>6.3</v>
       </c>
       <c r="C3" s="4">
-        <v>6.3</v>
-      </c>
-      <c r="D3" s="4">
         <v>228.5</v>
       </c>
+      <c r="D3" s="3">
+        <v>2488.9</v>
+      </c>
       <c r="E3" s="3">
-        <v>2488.9</v>
-      </c>
-      <c r="F3" s="3">
         <v>2952.8999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2002</v>
       </c>
-      <c r="B4" s="3">
-        <v>22556</v>
+      <c r="B4" s="4">
+        <v>4.4000000000000004</v>
       </c>
       <c r="C4" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D4" s="4">
         <v>268.89999999999998</v>
       </c>
+      <c r="D4" s="3">
+        <v>3262.7</v>
+      </c>
       <c r="E4" s="3">
-        <v>3262.7</v>
-      </c>
-      <c r="F4" s="3">
         <v>4222.7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2003</v>
       </c>
-      <c r="B5" s="3">
-        <v>27619</v>
+      <c r="B5" s="4">
+        <v>15.7</v>
       </c>
       <c r="C5" s="4">
-        <v>15.7</v>
-      </c>
-      <c r="D5" s="4">
         <v>302.3</v>
       </c>
+      <c r="D5" s="3">
+        <v>3804</v>
+      </c>
       <c r="E5" s="3">
-        <v>3804</v>
-      </c>
-      <c r="F5" s="3">
         <v>5767.7999999999993</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2004</v>
       </c>
-      <c r="B6" s="3">
-        <v>32032</v>
+      <c r="B6" s="4">
+        <v>12.5</v>
       </c>
       <c r="C6" s="4">
-        <v>12.5</v>
-      </c>
-      <c r="D6" s="4">
         <v>470.3</v>
       </c>
+      <c r="D6" s="3">
+        <v>5313.1</v>
+      </c>
       <c r="E6" s="3">
-        <v>5313.1</v>
-      </c>
-      <c r="F6" s="3">
         <v>8019.3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2005</v>
       </c>
-      <c r="B7" s="3">
-        <v>37652</v>
+      <c r="B7" s="4">
+        <v>10</v>
       </c>
       <c r="C7" s="4">
-        <v>10</v>
-      </c>
-      <c r="D7" s="4">
         <v>597.4</v>
       </c>
+      <c r="D7" s="3">
+        <v>7002.9</v>
+      </c>
       <c r="E7" s="3">
-        <v>7002.9</v>
-      </c>
-      <c r="F7" s="3">
         <v>11255.4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2006</v>
       </c>
-      <c r="B8" s="3">
-        <v>44754.366999999998</v>
+      <c r="B8" s="4">
+        <v>14.1</v>
       </c>
       <c r="C8" s="4">
-        <v>14.1</v>
-      </c>
-      <c r="D8" s="4">
         <v>775.3</v>
       </c>
+      <c r="D8" s="3">
+        <v>6512.3</v>
+      </c>
       <c r="E8" s="3">
-        <v>6512.3</v>
-      </c>
-      <c r="F8" s="3">
         <v>14397.2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2007</v>
       </c>
-      <c r="B9" s="3">
-        <v>53429.599999999999</v>
+      <c r="B9" s="4">
+        <v>13.1</v>
       </c>
       <c r="C9" s="4">
-        <v>13.1</v>
-      </c>
-      <c r="D9" s="4">
         <v>1333.69</v>
       </c>
+      <c r="D9" s="3">
+        <v>9537.2000000000007</v>
+      </c>
       <c r="E9" s="3">
-        <v>9537.2000000000007</v>
-      </c>
-      <c r="F9" s="3">
         <v>20661.900000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2008</v>
       </c>
-      <c r="B10" s="3">
-        <v>62922</v>
+      <c r="B10" s="4">
+        <v>7.3</v>
       </c>
       <c r="C10" s="4">
-        <v>7.3</v>
-      </c>
-      <c r="D10" s="4">
         <v>1672.4</v>
       </c>
+      <c r="D10" s="3">
+        <v>11633.6</v>
+      </c>
       <c r="E10" s="3">
-        <v>11633.6</v>
-      </c>
-      <c r="F10" s="3">
         <v>24085.200000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2009</v>
       </c>
-      <c r="B11" s="3">
-        <v>60430</v>
+      <c r="B11" s="4">
+        <v>0.4</v>
       </c>
       <c r="C11" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="D11" s="4">
         <v>1480.25</v>
       </c>
+      <c r="D11" s="3">
+        <v>10456.299999999999</v>
+      </c>
       <c r="E11" s="3">
-        <v>10456.299999999999</v>
-      </c>
-      <c r="F11" s="3">
         <v>23834.05</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2010</v>
       </c>
-      <c r="B12" s="3">
-        <v>86275.376999999993</v>
+      <c r="B12" s="4">
+        <v>8.1</v>
       </c>
       <c r="C12" s="4">
-        <v>8.1</v>
-      </c>
-      <c r="D12" s="4">
         <v>1717.7</v>
       </c>
+      <c r="D12" s="3">
+        <v>12115</v>
+      </c>
       <c r="E12" s="3">
-        <v>12115</v>
-      </c>
-      <c r="F12" s="3">
         <v>26942.3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2011</v>
       </c>
-      <c r="B13" s="3">
-        <v>98772.813999999998</v>
+      <c r="B13" s="4">
+        <v>7.8</v>
       </c>
       <c r="C13" s="4">
-        <v>7.8</v>
-      </c>
-      <c r="D13" s="4">
         <v>1965.3</v>
       </c>
+      <c r="D13" s="3">
+        <v>14345.2</v>
+      </c>
       <c r="E13" s="3">
-        <v>14345.2</v>
-      </c>
-      <c r="F13" s="3">
         <v>30112.100000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2012</v>
       </c>
-      <c r="B14" s="3">
-        <v>105480.18399999999</v>
+      <c r="B14" s="4">
+        <v>4.0999999999999996</v>
       </c>
       <c r="C14" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="D14" s="4">
         <v>2515.0012200000001</v>
       </c>
+      <c r="D14" s="3">
+        <v>17633.5</v>
+      </c>
       <c r="E14" s="3">
-        <v>17633.5</v>
-      </c>
-      <c r="F14" s="3">
         <v>36272.300000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2013</v>
       </c>
-      <c r="B15" s="3">
-        <v>119532.871</v>
+      <c r="B15" s="4">
+        <v>5.2</v>
       </c>
       <c r="C15" s="4">
-        <v>5.2</v>
-      </c>
-      <c r="D15" s="4">
         <v>2820.6329099999998</v>
       </c>
+      <c r="D15" s="3">
+        <v>23254.2</v>
+      </c>
       <c r="E15" s="3">
-        <v>23254.2</v>
-      </c>
-      <c r="F15" s="3">
         <v>45081.100000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2014</v>
       </c>
-      <c r="B16" s="3">
-        <v>131964.258</v>
+      <c r="B16" s="4">
+        <v>4.7</v>
       </c>
       <c r="C16" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="D16" s="4">
         <v>2156.6</v>
       </c>
+      <c r="D16" s="3">
+        <v>22273.9</v>
+      </c>
       <c r="E16" s="3">
-        <v>22273.9</v>
-      </c>
-      <c r="F16" s="3">
         <v>48464.35</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2015</v>
       </c>
-      <c r="B17" s="3">
-        <v>146740.20499999999</v>
+      <c r="B17" s="4">
+        <v>13.6</v>
       </c>
       <c r="C17" s="4">
-        <v>13.6</v>
-      </c>
-      <c r="D17" s="4">
         <v>1756.8</v>
       </c>
+      <c r="D17" s="3">
+        <v>29689.13</v>
+      </c>
       <c r="E17" s="3">
-        <v>29689.13</v>
-      </c>
-      <c r="F17" s="3">
         <v>48496</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2016</v>
       </c>
-      <c r="B18" s="3">
-        <v>159010.41899999999</v>
+      <c r="B18" s="4">
+        <v>2.4</v>
       </c>
       <c r="C18" s="4">
-        <v>2.4</v>
-      </c>
-      <c r="D18" s="4">
         <v>2205.9</v>
       </c>
+      <c r="D18" s="3">
+        <v>33276.5</v>
+      </c>
       <c r="E18" s="3">
-        <v>33276.5</v>
-      </c>
-      <c r="F18" s="3">
         <v>53233.57</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2017</v>
       </c>
-      <c r="B19" s="3">
-        <v>176007.29300000001</v>
+      <c r="B19" s="4">
+        <v>7.3</v>
       </c>
       <c r="C19" s="4">
-        <v>7.3</v>
-      </c>
-      <c r="D19" s="4">
         <v>2803.3</v>
       </c>
+      <c r="D19" s="3">
+        <v>36996.959999999999</v>
+      </c>
       <c r="E19" s="3">
-        <v>36996.959999999999</v>
-      </c>
-      <c r="F19" s="3">
         <v>58003.299999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2018</v>
       </c>
-      <c r="B20" s="3">
-        <v>189062.62700000001</v>
+      <c r="B20" s="4">
+        <v>0.9</v>
       </c>
       <c r="C20" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="D20" s="4">
         <v>2995.2</v>
       </c>
+      <c r="D20" s="3">
+        <v>43556.94</v>
+      </c>
       <c r="E20" s="3">
-        <v>43556.94</v>
-      </c>
-      <c r="F20" s="3">
         <v>62116.58</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2019</v>
       </c>
-      <c r="B21" s="3">
-        <v>206256.239</v>
+      <c r="B21" s="4">
+        <v>7.5</v>
       </c>
       <c r="C21" s="4">
-        <v>7.5</v>
-      </c>
-      <c r="D21" s="4">
         <v>3059.6</v>
       </c>
+      <c r="D21" s="3">
+        <v>46851</v>
+      </c>
       <c r="E21" s="3">
-        <v>46851</v>
-      </c>
-      <c r="F21" s="3">
         <v>66997.459999999992</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2020</v>
       </c>
-      <c r="B22" s="3">
-        <v>199733.68400000001</v>
+      <c r="B22" s="4">
+        <v>0.39</v>
       </c>
       <c r="C22" s="4">
-        <v>0.39</v>
-      </c>
-      <c r="D22" s="4">
         <v>3783.54</v>
       </c>
+      <c r="D22" s="3">
+        <v>55638.74</v>
+      </c>
       <c r="E22" s="3">
-        <v>55638.74</v>
-      </c>
-      <c r="F22" s="3">
         <v>77805.990000000005</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2021</v>
       </c>
-      <c r="B23" s="3">
-        <v>242078.6</v>
+      <c r="B23" s="4">
+        <v>13.94</v>
       </c>
       <c r="C23" s="4">
-        <v>13.94</v>
-      </c>
-      <c r="D23" s="4">
         <v>3901.88</v>
       </c>
+      <c r="D23" s="3">
+        <v>57548.22</v>
+      </c>
       <c r="E23" s="3">
-        <v>57548.22</v>
-      </c>
-      <c r="F23" s="3">
         <v>88061.85</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2022</v>
       </c>
-      <c r="B24" s="3">
-        <v>274488.06300000002</v>
+      <c r="B24" s="4">
+        <v>30.2</v>
       </c>
       <c r="C24" s="4">
-        <v>30.2</v>
-      </c>
-      <c r="D24" s="4">
         <v>4474.17</v>
       </c>
+      <c r="D24" s="3">
+        <v>74979.64</v>
+      </c>
       <c r="E24" s="3">
-        <v>74979.64</v>
-      </c>
-      <c r="F24" s="3">
         <v>91680.93</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2023</v>
       </c>
-      <c r="B25" s="3">
-        <v>303554.037962</v>
+      <c r="B25" s="4">
+        <v>4.2</v>
       </c>
       <c r="C25" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="D25" s="4">
         <v>5453.14</v>
       </c>
+      <c r="D25" s="3">
+        <v>82370.97</v>
+      </c>
       <c r="E25" s="3">
-        <v>82370.97</v>
-      </c>
-      <c r="F25" s="3">
         <v>110614.53</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2024</v>
       </c>
-      <c r="B26" s="3">
-        <v>323816.82435722998</v>
+      <c r="B26" s="4">
+        <v>6.97</v>
       </c>
       <c r="C26" s="4">
-        <v>6.97</v>
-      </c>
-      <c r="D26" s="4">
         <v>5483.57</v>
       </c>
+      <c r="D26" s="3">
+        <v>82623.75</v>
+      </c>
       <c r="E26" s="3">
-        <v>82623.75</v>
-      </c>
-      <c r="F26" s="3">
         <v>125493.81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="4">
+        <v>6.84</v>
+      </c>
+      <c r="C27" s="4">
+        <v>5104.2700000000004</v>
+      </c>
+      <c r="D27" s="3">
+        <v>87029.67</v>
+      </c>
+      <c r="E27" s="3">
+        <v>140341.78</v>
       </c>
     </row>
   </sheetData>

--- a/data/Date_Sector_Monetar.xlsx
+++ b/data/Date_Sector_Monetar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/air/Desktop/FrameworkData-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B2AAAF-C174-AC40-A8FD-CCA8D88B5527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BEEED2-6871-E748-8883-10FA5AD5E150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monetar" sheetId="6" r:id="rId1"/>
@@ -166,7 +166,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -177,13 +177,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +417,7 @@
     <col min="18" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="8" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
